--- a/submission/workbook/IncuBrix_2027_Growth_Engineer_Option_3_AEO_SEO_GEO_Submission_Workbook.xlsx
+++ b/submission/workbook/IncuBrix_2027_Growth_Engineer_Option_3_AEO_SEO_GEO_Submission_Workbook.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t>GROWTH-ENG-2027-OPT3-001</t>
+          <t>VARNIKA S R</t>
         </is>
       </c>
       <c r="D5" s="24" t="n">
@@ -642,7 +642,7 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>Growth Engineer Candidate</t>
+          <t>VARNIKA S R</t>
         </is>
       </c>
       <c r="D6" s="24" t="n">
@@ -667,7 +667,7 @@
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t>candidate@incubrix.com</t>
+          <t>srvarnika7@gmail.com</t>
         </is>
       </c>
       <c r="D7" s="24" t="n">
@@ -692,7 +692,7 @@
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t>B.Tech Computer Science &amp; Engineering / AI &amp; Data Science</t>
+          <t>Btech IT</t>
         </is>
       </c>
       <c r="D8" s="24" t="n">
@@ -717,7 +717,7 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>2026-10-24 09:00 IST</t>
+          <t>24.10.26</t>
         </is>
       </c>
       <c r="D9" s="24" t="n">
@@ -742,7 +742,7 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>2026-10-31 22:00 IST</t>
+          <t>31.10.26</t>
         </is>
       </c>
       <c r="D10" s="24" t="n">
@@ -767,7 +767,7 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>submission/</t>
+          <t>https://github.com/Varnika2005/Incubrix2/tree/main/submission</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/incubrix/aeo-seo-geo-visibility-engine</t>
+          <t>https://github.com/Varnika2005/Incubrix2.git</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>submission/launch_kit/90_DAY_LAUNCH_KIT.md</t>
+          <t>https://github.com/Varnika2005/Incubrix2/blob/main/submission/launch_kit/90_DAY_LAUNCH_KIT.md</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>submission/videos/PRODUCT_WALKTHROUGH.mp4</t>
+          <t>https://drive.google.com/drive/folders/1_zW9sUntcIPquDLOnucu6LxumG-ddgFI?usp=sharing</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>submission/videos/TECHNICAL_DEMO.mp4</t>
+          <t>https://drive.google.com/drive/folders/1_zW9sUntcIPquDLOnucu6LxumG-ddgFI?usp=sharing</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Google Gemini 3.5 Flash Lite (live API), Claude 3.5 Sonnet &amp; OpenAI GPT-4o (research benchmarking), SerpApi &amp; Google CSE (SERP integration design), Python standard library, Node.js SQLite WAL, Playwright, React 19, Tailwind CSS v4</t>
+          <t>Google Gemini 2.5 Flash, OpenAI GPT-4o / ChatGPT, Claude 3.5 Sonnet, Perplexity Sonar, Python, Node.js SQLite WAL, Playwright, React 19, Tailwind CSS v4</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>$0.00 (Zero paid tools required; free-tier APIs and standard libraries used exclusively)</t>
+          <t>$0.00 (Zero paid tools; free-tier APIs and standard libraries used exclusively)</t>
         </is>
       </c>
     </row>
@@ -24078,13 +24078,19 @@
           <t>6 merged variants</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="G18" s="23" t="n"/>
-      <c r="H18" s="23" t="n"/>
+      <c r="F18" s="23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>logs/engine_runs.log &amp; exports/visibility.csv</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="15">
       <c r="A19" s="22" t="inlineStr">
@@ -24112,13 +24118,19 @@
           <t>0 new (idempotent)</t>
         </is>
       </c>
-      <c r="F19" s="23" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="G19" s="23" t="n"/>
-      <c r="H19" s="23" t="n"/>
+      <c r="F19" s="23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="H19" s="23" t="inlineStr">
+        <is>
+          <t>logs/engine_runs.log (identical row counts)</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="15">
       <c r="A20" s="22" t="inlineStr">
@@ -24146,13 +24158,19 @@
           <t>1 duplicate merged</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="G20" s="23" t="n"/>
-      <c r="H20" s="23" t="n"/>
+      <c r="F20" s="23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>logs/engine_runs.log (incremental upsert)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="15">
       <c r="A21" s="22" t="inlineStr">
@@ -24180,13 +24198,19 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="G21" s="23" t="n"/>
-      <c r="H21" s="23" t="n"/>
+      <c r="F21" s="23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="H21" s="23" t="inlineStr">
+        <is>
+          <t>logs/engine_runs.log (graceful retry/catch)</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="15">
       <c r="A23" s="20" t="inlineStr">
@@ -24353,8 +24377,8 @@
     <mergeCell ref="B28:H28"/>
     <mergeCell ref="B26:H26"/>
     <mergeCell ref="B27:H27"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A16:H16"/>
     <mergeCell ref="B24:H24"/>
     <mergeCell ref="B30:H30"/>
     <mergeCell ref="B29:H29"/>
